--- a/datos/red-pot-kennedy-visor.xlsx
+++ b/datos/red-pot-kennedy-visor.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1693" uniqueCount="1153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1696" uniqueCount="1156">
   <si>
     <t>RED POT KENNEDY - DATOS DEL VISOR 3D</t>
   </si>
@@ -42,6 +42,9 @@
     <t>NODOS: un nodo por fila. "Capa" debe ser exactamente el nombre de una fila de CAPAS (lista desplegable). "Imagen" es opcional (URL); si va vacia el visor dibuja la insignia con el ID.</t>
   </si>
   <si>
+    <t>Latitud/Longitud (NODOS): coordenadas WGS84 APROXIMADAS dentro de Kennedy; el modo Territorio ubica cada nodo con ellas (limites del mapa: lat 4.611-4.661, lon -74.178 a -74.132). Ajustelas si tiene el punto exacto.</t>
+  </si>
+  <si>
     <t>ARISTAS: origen/destino por ID de nodo; "Tipo" exactamente un nombre de INTERACCIONES (lista desplegable). Peso 1-4 (Media=1, Alta=2, Severa=3, Critica=4).</t>
   </si>
   <si>
@@ -358,6 +361,12 @@
   </si>
   <si>
     <t>Imagen (img, opcional)</t>
+  </si>
+  <si>
+    <t>Latitud</t>
+  </si>
+  <si>
+    <t>Longitud</t>
   </si>
   <si>
     <t>NOD-AE09</t>
@@ -3942,7 +3951,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="140" customWidth="1"/>
@@ -4005,12 +4014,17 @@
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>10</v>
+    <row r="14" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -4033,182 +4047,182 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -4231,155 +4245,155 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -4391,7 +4405,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L59"/>
+  <dimension ref="A1:N59"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -4404,2252 +4418,2607 @@
     <col min="10" max="10" width="50" customWidth="1"/>
     <col min="11" max="11" width="26" customWidth="1"/>
     <col min="12" max="12" width="22" customWidth="1"/>
+    <col min="13" max="14" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+        <v>114</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B2" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D2" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="E2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F2" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="G2" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="H2" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="I2" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="J2" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="K2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="L2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M2">
+        <v>4.656</v>
+      </c>
+      <c r="N2">
+        <v>-74.14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B3" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D3" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F3" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="G3" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="H3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="I3" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="J3" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="K3" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="L3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M3">
+        <v>4.63</v>
+      </c>
+      <c r="N3">
+        <v>-74.157</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B4" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D4" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E4" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="F4" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="G4" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="H4" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="I4" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="J4" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="K4" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="L4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M4">
+        <v>4.615</v>
+      </c>
+      <c r="N4">
+        <v>-74.174</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B5" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D5" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E5" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="F5" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="G5" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="H5" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="I5" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="J5" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="K5" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="L5" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M5">
+        <v>4.6255</v>
+      </c>
+      <c r="N5">
+        <v>-74.16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B6" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D6" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E6" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="F6" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="G6" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="H6" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="I6" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="J6" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K6" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="L6" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M6">
+        <v>4.636</v>
+      </c>
+      <c r="N6">
+        <v>-74.153</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B7" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D7" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E7" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="F7" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="G7" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="H7" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="I7" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="J7" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="K7" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="L7" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M7">
+        <v>4.6249</v>
+      </c>
+      <c r="N7">
+        <v>-74.162</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B8" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D8" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E8" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="F8" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="G8" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="H8" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="I8" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="J8" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="K8" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="L8" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M8">
+        <v>4.6419</v>
+      </c>
+      <c r="N8">
+        <v>-74.1478</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B9" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D9" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E9" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="F9" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="G9" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="H9" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="I9" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="J9" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="K9" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="L9" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M9">
+        <v>4.6262</v>
+      </c>
+      <c r="N9">
+        <v>-74.1514</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="B10" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D10" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E10" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="F10" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="G10" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="H10" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="I10" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="J10" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="K10" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="L10" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M10">
+        <v>4.612</v>
+      </c>
+      <c r="N10">
+        <v>-74.176</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B11" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="C11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D11" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="E11" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F11" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="G11" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="H11" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="I11" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="J11" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="K11" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="L11" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M11">
+        <v>4.63</v>
+      </c>
+      <c r="N11">
+        <v>-74.15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B12" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D12" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="E12" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F12" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="G12" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="H12" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="I12" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="J12" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="K12" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="L12" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M12">
+        <v>4.633</v>
+      </c>
+      <c r="N12">
+        <v>-74.144</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B13" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D13" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="E13" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F13" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="G13" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="H13" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="I13" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="J13" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="K13" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L13" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M13">
+        <v>4.635</v>
+      </c>
+      <c r="N13">
+        <v>-74.1545</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B14" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="C14" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D14" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="E14" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F14" t="s">
+        <v>225</v>
+      </c>
+      <c r="G14" t="s">
+        <v>226</v>
+      </c>
+      <c r="H14" t="s">
+        <v>227</v>
+      </c>
+      <c r="I14" t="s">
+        <v>228</v>
+      </c>
+      <c r="J14" t="s">
+        <v>229</v>
+      </c>
+      <c r="K14" t="s">
         <v>222</v>
-      </c>
-      <c r="G14" t="s">
-        <v>223</v>
-      </c>
-      <c r="H14" t="s">
-        <v>224</v>
-      </c>
-      <c r="I14" t="s">
-        <v>225</v>
-      </c>
-      <c r="J14" t="s">
-        <v>226</v>
-      </c>
-      <c r="K14" t="s">
-        <v>219</v>
       </c>
       <c r="L14" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M14">
+        <v>4.633</v>
+      </c>
+      <c r="N14">
+        <v>-74.138</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B15" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="C15" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D15" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="E15" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F15" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="G15" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="H15" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="I15" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="J15" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="K15" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="L15" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M15">
+        <v>4.629</v>
+      </c>
+      <c r="N15">
+        <v>-74.159</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="B16" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C16" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D16" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="E16" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="F16" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="G16" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="H16" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="I16" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="J16" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="K16" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="L16" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M16">
+        <v>4.614</v>
+      </c>
+      <c r="N16">
+        <v>-74.17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="B17" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D17" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="E17" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F17" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="G17" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="H17" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="I17" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="J17" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="K17" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="L17" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M17">
+        <v>4.6225</v>
+      </c>
+      <c r="N17">
+        <v>-74.159</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="B18" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="C18" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D18" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="E18" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F18" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="G18" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H18" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="I18" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="J18" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="K18" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="L18" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M18">
+        <v>4.64</v>
+      </c>
+      <c r="N18">
+        <v>-74.14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B19" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C19" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D19" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="E19" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="F19" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="G19" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="H19" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="I19" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="J19" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="K19" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="L19" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M19">
+        <v>4.621</v>
+      </c>
+      <c r="N19">
+        <v>-74.154</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B20" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="C20" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D20" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="E20" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="F20" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="G20" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="H20" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="I20" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="J20" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="K20" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="L20" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M20">
+        <v>4.623</v>
+      </c>
+      <c r="N20">
+        <v>-74.148</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B21" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C21" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D21" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="E21" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="F21" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="G21" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="H21" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I21" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="J21" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="K21" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="L21" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M21">
+        <v>4.6335</v>
+      </c>
+      <c r="N21">
+        <v>-74.155</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B22" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="C22" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D22" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="E22" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="F22" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="G22" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="H22" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="I22" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="J22" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="K22" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="L22" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M22">
+        <v>4.6365</v>
+      </c>
+      <c r="N22">
+        <v>-74.152</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="B23" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="C23" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D23" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="E23" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="F23" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="G23" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="H23" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="I23" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="J23" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="K23" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="L23" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M23">
+        <v>4.637</v>
+      </c>
+      <c r="N23">
+        <v>-74.154</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="B24" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C24" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D24" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="E24" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="F24" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="G24" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="H24" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="I24" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="J24" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="K24" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="L24" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M24">
+        <v>4.626</v>
+      </c>
+      <c r="N24">
+        <v>-74.156</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="B25" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C25" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D25" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="E25" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="F25" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="G25" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="H25" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="I25" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="J25" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="K25" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="L25" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M25">
+        <v>4.6355</v>
+      </c>
+      <c r="N25">
+        <v>-74.1535</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="B26" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C26" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D26" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="E26" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="F26" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="G26" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="H26" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="I26" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="J26" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="K26" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="L26" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M26">
+        <v>4.6345</v>
+      </c>
+      <c r="N26">
+        <v>-74.15</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B27" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C27" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D27" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="E27" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="F27" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="G27" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="H27" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="I27" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="J27" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="K27" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="L27" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M27">
+        <v>4.6245</v>
+      </c>
+      <c r="N27">
+        <v>-74.161</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B28" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="C28" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D28" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="E28" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F28" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G28" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="H28" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="I28" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="J28" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="K28" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="L28" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M28">
+        <v>4.634</v>
+      </c>
+      <c r="N28">
+        <v>-74.156</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="B29" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="C29" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D29" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="E29" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F29" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="G29" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="H29" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="I29" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="J29" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="K29" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="L29" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M29">
+        <v>4.626</v>
+      </c>
+      <c r="N29">
+        <v>-74.145</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="B30" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="C30" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D30" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="E30" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F30" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="G30" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="H30" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="I30" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="J30" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="K30" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="L30" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M30">
+        <v>4.631</v>
+      </c>
+      <c r="N30">
+        <v>-74.16</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B31" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="C31" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D31" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="E31" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F31" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="G31" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="H31" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="I31" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="J31" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="K31" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="L31" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M31">
+        <v>4.638</v>
+      </c>
+      <c r="N31">
+        <v>-74.15</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B32" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="C32" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D32" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="E32" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="F32" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="G32" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="H32" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="I32" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="J32" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="K32" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="L32" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M32">
+        <v>4.627</v>
+      </c>
+      <c r="N32">
+        <v>-74.148</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="B33" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="C33" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D33" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="E33" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="F33" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="G33" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="H33" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="I33" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="J33" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="K33" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="L33" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M33">
+        <v>4.6285</v>
+      </c>
+      <c r="N33">
+        <v>-74.153</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B34" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="C34" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D34" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="E34" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="F34" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="G34" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="H34" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="I34" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="J34" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="K34" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="L34" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M34">
+        <v>4.6125</v>
+      </c>
+      <c r="N34">
+        <v>-74.155</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="B35" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="C35" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D35" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="E35" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="F35" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="G35" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="H35" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="I35" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="J35" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="K35" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="L35" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M35">
+        <v>4.646</v>
+      </c>
+      <c r="N35">
+        <v>-74.145</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="B36" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="C36" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D36" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E36" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="F36" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="G36" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="H36" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="I36" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="J36" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="K36" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="L36" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M36">
+        <v>4.63</v>
+      </c>
+      <c r="N36">
+        <v>-74.1575</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="B37" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="C37" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D37" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="E37" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="F37" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="G37" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="H37" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="I37" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="J37" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="K37" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="L37" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M37">
+        <v>4.6215</v>
+      </c>
+      <c r="N37">
+        <v>-74.149</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="B38" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="C38" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D38" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="E38" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="F38" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="G38" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="H38" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="I38" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="J38" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="K38" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="L38" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M38">
+        <v>4.617</v>
+      </c>
+      <c r="N38">
+        <v>-74.17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="B39" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="C39" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D39" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="E39" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F39" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="G39" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="H39" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="I39" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="J39" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="K39" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="L39" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M39">
+        <v>4.634</v>
+      </c>
+      <c r="N39">
+        <v>-74.1595</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="B40" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="C40" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D40" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="E40" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="F40" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="G40" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="H40" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="I40" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="J40" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="K40" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="L40" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M40">
+        <v>4.62</v>
+      </c>
+      <c r="N40">
+        <v>-74.152</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="B41" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="C41" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D41" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="E41" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="F41" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="G41" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="H41" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="I41" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="J41" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="K41" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="L41" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M41">
+        <v>4.624</v>
+      </c>
+      <c r="N41">
+        <v>-74.144</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="B42" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="C42" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D42" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="E42" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F42" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="G42" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="H42" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="I42" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="J42" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="K42" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="L42" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M42">
+        <v>4.631</v>
+      </c>
+      <c r="N42">
+        <v>-74.137</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="B43" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="C43" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D43" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="E43" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F43" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="G43" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="H43" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="I43" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="J43" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="K43" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="L43" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M43">
+        <v>4.613</v>
+      </c>
+      <c r="N43">
+        <v>-74.15</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="B44" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="C44" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D44" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="E44" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F44" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="G44" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="H44" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="I44" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="J44" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="K44" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="L44" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M44">
+        <v>4.619</v>
+      </c>
+      <c r="N44">
+        <v>-74.159</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="B45" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="C45" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D45" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="E45" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F45" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="G45" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="H45" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="I45" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="J45" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="K45" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="L45" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M45">
+        <v>4.632</v>
+      </c>
+      <c r="N45">
+        <v>-74.142</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="B46" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="C46" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D46" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="E46" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F46" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="G46" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="H46" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="I46" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="J46" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="K46" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="L46" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M46">
+        <v>4.645</v>
+      </c>
+      <c r="N46">
+        <v>-74.145</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="B47" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="C47" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D47" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="E47" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="F47" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="G47" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="H47" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="I47" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="J47" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="K47" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="L47" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M47">
+        <v>4.6368</v>
+      </c>
+      <c r="N47">
+        <v>-74.1522</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="B48" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="C48" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D48" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="E48" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="F48" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="G48" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="H48" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="I48" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="J48" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="K48" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="L48" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M48">
+        <v>4.64</v>
+      </c>
+      <c r="N48">
+        <v>-74.15</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="B49" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="C49" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D49" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="E49" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F49" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="G49" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="H49" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="I49" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="J49" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="K49" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="L49" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M49">
+        <v>4.654</v>
+      </c>
+      <c r="N49">
+        <v>-74.145</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="B50" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="C50" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D50" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="E50" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F50" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="G50" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="H50" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="I50" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="J50" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="K50" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="L50" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M50">
+        <v>4.631</v>
+      </c>
+      <c r="N50">
+        <v>-74.163</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="B51" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="C51" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D51" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="E51" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="F51" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="G51" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="H51" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="I51" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="J51" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="K51" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="L51" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M51">
+        <v>4.611</v>
+      </c>
+      <c r="N51">
+        <v>-74.173</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="B52" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="C52" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D52" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="E52" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="F52" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="G52" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="H52" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="I52" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="J52" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="K52" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="L52" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M52">
+        <v>4.62</v>
+      </c>
+      <c r="N52">
+        <v>-74.17</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="B53" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="C53" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D53" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="E53" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F53" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="G53" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="H53" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="I53" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="J53" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="K53" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="L53" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M53">
+        <v>4.6335</v>
+      </c>
+      <c r="N53">
+        <v>-74.1465</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="B54" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="C54" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D54" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="E54" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F54" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="G54" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="H54" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="I54" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="J54" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="K54" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="L54" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M54">
+        <v>4.628</v>
+      </c>
+      <c r="N54">
+        <v>-74.14</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="B55" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="C55" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D55" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="E55" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="F55" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="G55" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="H55" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="I55" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="J55" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="K55" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="L55" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M55">
+        <v>4.614</v>
+      </c>
+      <c r="N55">
+        <v>-74.171</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="B56" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="C56" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D56" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="E56" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="F56" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="G56" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="H56" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="I56" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="J56" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="K56" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="L56" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M56">
+        <v>4.6352</v>
+      </c>
+      <c r="N56">
+        <v>-74.1508</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="B57" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="C57" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D57" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="E57" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="F57" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="G57" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="H57" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="I57" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="J57" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="K57" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="L57" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M57">
+        <v>4.6365</v>
+      </c>
+      <c r="N57">
+        <v>-74.155</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="B58" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="C58" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D58" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="E58" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="F58" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="G58" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="H58" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="I58" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="J58" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="K58" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="L58" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M58">
+        <v>4.6245</v>
+      </c>
+      <c r="N58">
+        <v>-74.16</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="B59" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="C59" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D59" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="E59" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F59" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="G59" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="H59" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="I59" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="J59" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="K59" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="L59" t="s">
         <v>1</v>
       </c>
+      <c r="M59">
+        <v>4.6235</v>
+      </c>
+      <c r="N59">
+        <v>-74.1565</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L1"/>
+  <autoFilter ref="A1:N1"/>
   <dataValidations count="1">
     <dataValidation type="list" sqref="C2:C259">
       <formula1>CAPAS!$B$2:$B$30</formula1>
@@ -6678,2966 +7047,2966 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="B2" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C2" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="D2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E2" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="F2" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="G2" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="H2">
         <v>2</v>
       </c>
       <c r="I2" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="J2" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="K2" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="L2" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="B3" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="D3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E3" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="F3" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="G3" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="H3">
         <v>3</v>
       </c>
       <c r="I3" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="J3" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="K3" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="L3" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="B4" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C4" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="D4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E4" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="F4" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="G4" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="H4">
         <v>1</v>
       </c>
       <c r="I4" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="J4" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="K4" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="L4" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="B5" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C5" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="D5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E5" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="F5" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="G5" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="H5">
         <v>4</v>
       </c>
       <c r="I5" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="J5" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="K5" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="L5" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="B6" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C6" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="D6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E6" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="F6" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="G6" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="H6">
         <v>2</v>
       </c>
       <c r="I6" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="J6" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="K6" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="L6" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="B7" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C7" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="D7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E7" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="F7" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="G7" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="H7">
         <v>1</v>
       </c>
       <c r="I7" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="J7" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="K7" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="L7" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="B8" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C8" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="D8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E8" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="F8" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="G8" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="H8">
         <v>2</v>
       </c>
       <c r="I8" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="J8" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="K8" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="L8" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="B9" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C9" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="D9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E9" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="F9" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="G9" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="H9">
         <v>1</v>
       </c>
       <c r="I9" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="J9" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="K9" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="L9" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="B10" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C10" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="D10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E10" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="F10" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="G10" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="H10">
         <v>3</v>
       </c>
       <c r="I10" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="J10" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="K10" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="L10" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="B11" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C11" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="D11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E11" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="F11" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="G11" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="H11">
         <v>2</v>
       </c>
       <c r="I11" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="J11" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="K11" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="L11" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="B12" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C12" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="D12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E12" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="F12" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="G12" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="H12">
         <v>4</v>
       </c>
       <c r="I12" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="J12" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="K12" t="s">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="L12" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="B13" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C13" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="D13" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E13" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="F13" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="G13" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="H13">
         <v>4</v>
       </c>
       <c r="I13" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="J13" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="K13" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="L13" t="s">
-        <v>700</v>
+        <v>703</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="B14" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C14" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="D14" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E14" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="F14" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="G14" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="H14">
         <v>2</v>
       </c>
       <c r="I14" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="J14" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="K14" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="L14" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="B15" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C15" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="D15" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E15" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="F15" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="G15" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="H15">
         <v>4</v>
       </c>
       <c r="I15" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="J15" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="K15" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="L15" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="B16" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C16" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="D16" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E16" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="F16" t="s">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="G16" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="H16">
         <v>3</v>
       </c>
       <c r="I16" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="J16" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="K16" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="L16" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="B17" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C17" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="D17" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E17" t="s">
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="F17" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="G17" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="H17">
         <v>4</v>
       </c>
       <c r="I17" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="J17" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="K17" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="L17" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="B18" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C18" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="D18" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E18" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="F18" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="G18" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="H18">
         <v>4</v>
       </c>
       <c r="I18" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="J18" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="K18" t="s">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="L18" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="B19" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C19" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="D19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E19" t="s">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="F19" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="G19" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="H19">
         <v>2</v>
       </c>
       <c r="I19" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="J19" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="K19" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="L19" t="s">
-        <v>742</v>
+        <v>745</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="B20" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="C20" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="D20" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E20" t="s">
-        <v>744</v>
+        <v>747</v>
       </c>
       <c r="F20" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="G20" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="H20">
         <v>3</v>
       </c>
       <c r="I20" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="J20" t="s">
-        <v>747</v>
+        <v>750</v>
       </c>
       <c r="K20" t="s">
-        <v>748</v>
+        <v>751</v>
       </c>
       <c r="L20" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="B21" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="C21" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D21" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E21" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="F21" t="s">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="G21" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="H21">
         <v>3</v>
       </c>
       <c r="I21" t="s">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="J21" t="s">
-        <v>754</v>
+        <v>757</v>
       </c>
       <c r="K21" t="s">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="L21" t="s">
-        <v>756</v>
+        <v>759</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="B22" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C22" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="D22" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E22" t="s">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="F22" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="G22" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="H22">
         <v>1</v>
       </c>
       <c r="I22" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="J22" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="K22" t="s">
-        <v>762</v>
+        <v>765</v>
       </c>
       <c r="L22" t="s">
-        <v>763</v>
+        <v>766</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="B23" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C23" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="D23" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E23" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="F23" t="s">
-        <v>766</v>
+        <v>769</v>
       </c>
       <c r="G23" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="H23">
         <v>2</v>
       </c>
       <c r="I23" t="s">
-        <v>767</v>
+        <v>770</v>
       </c>
       <c r="J23" t="s">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="K23" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="L23" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="B24" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C24" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="D24" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E24" t="s">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="F24" t="s">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="G24" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="H24">
         <v>2</v>
       </c>
       <c r="I24" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="J24" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="K24" t="s">
-        <v>775</v>
+        <v>778</v>
       </c>
       <c r="L24" t="s">
-        <v>776</v>
+        <v>779</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="B25" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="C25" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="D25" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E25" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="F25" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="G25" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="H25">
         <v>1</v>
       </c>
       <c r="I25" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="J25" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="K25" t="s">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="L25" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>784</v>
+        <v>787</v>
       </c>
       <c r="B26" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="C26" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="D26" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E26" t="s">
-        <v>785</v>
+        <v>788</v>
       </c>
       <c r="F26" t="s">
-        <v>786</v>
+        <v>789</v>
       </c>
       <c r="G26" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="H26">
         <v>4</v>
       </c>
       <c r="I26" t="s">
-        <v>787</v>
+        <v>790</v>
       </c>
       <c r="J26" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="K26" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="L26" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>791</v>
+        <v>794</v>
       </c>
       <c r="B27" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="C27" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="D27" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E27" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="F27" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="G27" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="H27">
         <v>3</v>
       </c>
       <c r="I27" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="J27" t="s">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="K27" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="L27" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="B28" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="C28" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="D28" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E28" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="F28" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="G28" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="H28">
         <v>4</v>
       </c>
       <c r="I28" t="s">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="J28" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="K28" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="L28" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="B29" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="C29" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="D29" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E29" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="F29" t="s">
-        <v>807</v>
+        <v>810</v>
       </c>
       <c r="G29" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="H29">
         <v>2</v>
       </c>
       <c r="I29" t="s">
-        <v>808</v>
+        <v>811</v>
       </c>
       <c r="J29" t="s">
-        <v>809</v>
+        <v>812</v>
       </c>
       <c r="K29" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="L29" t="s">
-        <v>811</v>
+        <v>814</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="B30" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="C30" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="D30" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E30" t="s">
-        <v>813</v>
+        <v>816</v>
       </c>
       <c r="F30" t="s">
-        <v>814</v>
+        <v>817</v>
       </c>
       <c r="G30" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="H30">
         <v>2</v>
       </c>
       <c r="I30" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="J30" t="s">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="K30" t="s">
-        <v>817</v>
+        <v>820</v>
       </c>
       <c r="L30" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>819</v>
+        <v>822</v>
       </c>
       <c r="B31" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="C31" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="D31" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E31" t="s">
-        <v>813</v>
+        <v>816</v>
       </c>
       <c r="F31" t="s">
-        <v>820</v>
+        <v>823</v>
       </c>
       <c r="G31" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="H31">
         <v>2</v>
       </c>
       <c r="I31" t="s">
-        <v>821</v>
+        <v>824</v>
       </c>
       <c r="J31" t="s">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="K31" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="L31" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="B32" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="C32" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="D32" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E32" t="s">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="F32" t="s">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="G32" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="H32">
         <v>1</v>
       </c>
       <c r="I32" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="J32" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="K32" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="L32" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="B33" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="C33" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="D33" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E33" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="F33" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="G33" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="H33">
         <v>3</v>
       </c>
       <c r="I33" t="s">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="J33" t="s">
-        <v>836</v>
+        <v>839</v>
       </c>
       <c r="K33" t="s">
-        <v>837</v>
+        <v>840</v>
       </c>
       <c r="L33" t="s">
-        <v>838</v>
+        <v>841</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
       <c r="B34" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="C34" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="D34" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E34" t="s">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="F34" t="s">
-        <v>841</v>
+        <v>844</v>
       </c>
       <c r="G34" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="H34">
         <v>2</v>
       </c>
       <c r="I34" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="J34" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="K34" t="s">
-        <v>844</v>
+        <v>847</v>
       </c>
       <c r="L34" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="B35" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="C35" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D35" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E35" t="s">
-        <v>847</v>
+        <v>850</v>
       </c>
       <c r="F35" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="G35" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="H35">
         <v>2</v>
       </c>
       <c r="I35" t="s">
-        <v>849</v>
+        <v>852</v>
       </c>
       <c r="J35" t="s">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="K35" t="s">
-        <v>851</v>
+        <v>854</v>
       </c>
       <c r="L35" t="s">
-        <v>852</v>
+        <v>855</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="B36" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="C36" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D36" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E36" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="F36" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="G36" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="H36">
         <v>1</v>
       </c>
       <c r="I36" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
       <c r="J36" t="s">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="K36" t="s">
-        <v>858</v>
+        <v>861</v>
       </c>
       <c r="L36" t="s">
-        <v>859</v>
+        <v>862</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="B37" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="C37" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="D37" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E37" t="s">
-        <v>861</v>
+        <v>864</v>
       </c>
       <c r="F37" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="G37" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="H37">
         <v>2</v>
       </c>
       <c r="I37" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
       <c r="J37" t="s">
-        <v>864</v>
+        <v>867</v>
       </c>
       <c r="K37" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="L37" t="s">
-        <v>866</v>
+        <v>869</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>867</v>
+        <v>870</v>
       </c>
       <c r="B38" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="C38" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="D38" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E38" t="s">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="F38" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="G38" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="H38">
         <v>2</v>
       </c>
       <c r="I38" t="s">
-        <v>870</v>
+        <v>873</v>
       </c>
       <c r="J38" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="K38" t="s">
-        <v>872</v>
+        <v>875</v>
       </c>
       <c r="L38" t="s">
-        <v>873</v>
+        <v>876</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>874</v>
+        <v>877</v>
       </c>
       <c r="B39" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C39" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="D39" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E39" t="s">
-        <v>875</v>
+        <v>878</v>
       </c>
       <c r="F39" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="G39" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="H39">
         <v>3</v>
       </c>
       <c r="I39" t="s">
-        <v>877</v>
+        <v>880</v>
       </c>
       <c r="J39" t="s">
-        <v>878</v>
+        <v>881</v>
       </c>
       <c r="K39" t="s">
-        <v>879</v>
+        <v>882</v>
       </c>
       <c r="L39" t="s">
-        <v>880</v>
+        <v>883</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>881</v>
+        <v>884</v>
       </c>
       <c r="B40" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C40" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="D40" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E40" t="s">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="F40" t="s">
-        <v>883</v>
+        <v>886</v>
       </c>
       <c r="G40" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="H40">
         <v>1</v>
       </c>
       <c r="I40" t="s">
-        <v>884</v>
+        <v>887</v>
       </c>
       <c r="J40" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="K40" t="s">
-        <v>886</v>
+        <v>889</v>
       </c>
       <c r="L40" t="s">
-        <v>887</v>
+        <v>890</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="B41" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C41" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="D41" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E41" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="F41" t="s">
-        <v>890</v>
+        <v>893</v>
       </c>
       <c r="G41" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="H41">
         <v>1</v>
       </c>
       <c r="I41" t="s">
-        <v>891</v>
+        <v>894</v>
       </c>
       <c r="J41" t="s">
-        <v>892</v>
+        <v>895</v>
       </c>
       <c r="K41" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="L41" t="s">
-        <v>894</v>
+        <v>897</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>895</v>
+        <v>898</v>
       </c>
       <c r="B42" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="C42" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="D42" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E42" t="s">
-        <v>896</v>
+        <v>899</v>
       </c>
       <c r="F42" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="G42" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="H42">
         <v>1</v>
       </c>
       <c r="I42" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="J42" t="s">
-        <v>899</v>
+        <v>902</v>
       </c>
       <c r="K42" t="s">
-        <v>900</v>
+        <v>903</v>
       </c>
       <c r="L42" t="s">
-        <v>901</v>
+        <v>904</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>902</v>
+        <v>905</v>
       </c>
       <c r="B43" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C43" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="D43" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E43" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="F43" t="s">
-        <v>904</v>
+        <v>907</v>
       </c>
       <c r="G43" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="H43">
         <v>2</v>
       </c>
       <c r="I43" t="s">
-        <v>905</v>
+        <v>908</v>
       </c>
       <c r="J43" t="s">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="K43" t="s">
-        <v>907</v>
+        <v>910</v>
       </c>
       <c r="L43" t="s">
-        <v>908</v>
+        <v>911</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>909</v>
+        <v>912</v>
       </c>
       <c r="B44" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C44" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="D44" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E44" t="s">
-        <v>910</v>
+        <v>913</v>
       </c>
       <c r="F44" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="G44" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="H44">
         <v>2</v>
       </c>
       <c r="I44" t="s">
-        <v>912</v>
+        <v>915</v>
       </c>
       <c r="J44" t="s">
-        <v>913</v>
+        <v>916</v>
       </c>
       <c r="K44" t="s">
-        <v>914</v>
+        <v>917</v>
       </c>
       <c r="L44" t="s">
-        <v>915</v>
+        <v>918</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>916</v>
+        <v>919</v>
       </c>
       <c r="B45" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="C45" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="D45" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E45" t="s">
-        <v>917</v>
+        <v>920</v>
       </c>
       <c r="F45" t="s">
-        <v>918</v>
+        <v>921</v>
       </c>
       <c r="G45" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="H45">
         <v>1</v>
       </c>
       <c r="I45" t="s">
-        <v>919</v>
+        <v>922</v>
       </c>
       <c r="J45" t="s">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="K45" t="s">
-        <v>921</v>
+        <v>924</v>
       </c>
       <c r="L45" t="s">
-        <v>922</v>
+        <v>925</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>923</v>
+        <v>926</v>
       </c>
       <c r="B46" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C46" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="D46" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E46" t="s">
-        <v>924</v>
+        <v>927</v>
       </c>
       <c r="F46" t="s">
-        <v>925</v>
+        <v>928</v>
       </c>
       <c r="G46" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="H46">
         <v>2</v>
       </c>
       <c r="I46" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="J46" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
       <c r="K46" t="s">
-        <v>928</v>
+        <v>931</v>
       </c>
       <c r="L46" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>930</v>
+        <v>933</v>
       </c>
       <c r="B47" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="C47" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="D47" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E47" t="s">
-        <v>931</v>
+        <v>934</v>
       </c>
       <c r="F47" t="s">
-        <v>932</v>
+        <v>935</v>
       </c>
       <c r="G47" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="H47">
         <v>3</v>
       </c>
       <c r="I47" t="s">
-        <v>933</v>
+        <v>936</v>
       </c>
       <c r="J47" t="s">
-        <v>934</v>
+        <v>937</v>
       </c>
       <c r="K47" t="s">
-        <v>935</v>
+        <v>938</v>
       </c>
       <c r="L47" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="B48" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C48" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="D48" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E48" t="s">
-        <v>937</v>
+        <v>940</v>
       </c>
       <c r="F48" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="G48" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="H48">
         <v>1</v>
       </c>
       <c r="I48" t="s">
-        <v>939</v>
+        <v>942</v>
       </c>
       <c r="J48" t="s">
-        <v>940</v>
+        <v>943</v>
       </c>
       <c r="K48" t="s">
-        <v>941</v>
+        <v>944</v>
       </c>
       <c r="L48" t="s">
-        <v>942</v>
+        <v>945</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>943</v>
+        <v>946</v>
       </c>
       <c r="B49" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C49" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="D49" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E49" t="s">
-        <v>944</v>
+        <v>947</v>
       </c>
       <c r="F49" t="s">
-        <v>945</v>
+        <v>948</v>
       </c>
       <c r="G49" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="H49">
         <v>1</v>
       </c>
       <c r="I49" t="s">
-        <v>946</v>
+        <v>949</v>
       </c>
       <c r="J49" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
       <c r="K49" t="s">
-        <v>948</v>
+        <v>951</v>
       </c>
       <c r="L49" t="s">
-        <v>949</v>
+        <v>952</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="B50" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="C50" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="D50" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E50" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="F50" t="s">
-        <v>952</v>
+        <v>955</v>
       </c>
       <c r="G50" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="H50">
         <v>1</v>
       </c>
       <c r="I50" t="s">
-        <v>953</v>
+        <v>956</v>
       </c>
       <c r="J50" t="s">
-        <v>954</v>
+        <v>957</v>
       </c>
       <c r="K50" t="s">
-        <v>955</v>
+        <v>958</v>
       </c>
       <c r="L50" t="s">
-        <v>956</v>
+        <v>959</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>957</v>
+        <v>960</v>
       </c>
       <c r="B51" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="C51" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="D51" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E51" t="s">
-        <v>958</v>
+        <v>961</v>
       </c>
       <c r="F51" t="s">
-        <v>959</v>
+        <v>962</v>
       </c>
       <c r="G51" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="H51">
         <v>1</v>
       </c>
       <c r="I51" t="s">
-        <v>960</v>
+        <v>963</v>
       </c>
       <c r="J51" t="s">
-        <v>961</v>
+        <v>964</v>
       </c>
       <c r="K51" t="s">
-        <v>962</v>
+        <v>965</v>
       </c>
       <c r="L51" t="s">
-        <v>963</v>
+        <v>966</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>964</v>
+        <v>967</v>
       </c>
       <c r="B52" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="C52" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="D52" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E52" t="s">
-        <v>965</v>
+        <v>968</v>
       </c>
       <c r="F52" t="s">
-        <v>966</v>
+        <v>969</v>
       </c>
       <c r="G52" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="H52">
         <v>2</v>
       </c>
       <c r="I52" t="s">
-        <v>967</v>
+        <v>970</v>
       </c>
       <c r="J52" t="s">
-        <v>968</v>
+        <v>971</v>
       </c>
       <c r="K52" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="L52" t="s">
-        <v>970</v>
+        <v>973</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>971</v>
+        <v>974</v>
       </c>
       <c r="B53" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="C53" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="D53" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E53" t="s">
-        <v>965</v>
+        <v>968</v>
       </c>
       <c r="F53" t="s">
-        <v>972</v>
+        <v>975</v>
       </c>
       <c r="G53" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="H53">
         <v>2</v>
       </c>
       <c r="I53" t="s">
-        <v>967</v>
+        <v>970</v>
       </c>
       <c r="J53" t="s">
-        <v>973</v>
+        <v>976</v>
       </c>
       <c r="K53" t="s">
-        <v>974</v>
+        <v>977</v>
       </c>
       <c r="L53" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>975</v>
+        <v>978</v>
       </c>
       <c r="B54" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="C54" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="D54" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E54" t="s">
-        <v>965</v>
+        <v>968</v>
       </c>
       <c r="F54" t="s">
-        <v>976</v>
+        <v>979</v>
       </c>
       <c r="G54" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="H54">
         <v>2</v>
       </c>
       <c r="I54" t="s">
-        <v>967</v>
+        <v>970</v>
       </c>
       <c r="J54" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
       <c r="K54" t="s">
-        <v>978</v>
+        <v>981</v>
       </c>
       <c r="L54" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>979</v>
+        <v>982</v>
       </c>
       <c r="B55" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="C55" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="D55" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E55" t="s">
-        <v>980</v>
+        <v>983</v>
       </c>
       <c r="F55" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="G55" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="H55">
         <v>3</v>
       </c>
       <c r="I55" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
       <c r="J55" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
       <c r="K55" t="s">
-        <v>984</v>
+        <v>987</v>
       </c>
       <c r="L55" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>986</v>
+        <v>989</v>
       </c>
       <c r="B56" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="C56" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D56" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E56" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="F56" t="s">
-        <v>988</v>
+        <v>991</v>
       </c>
       <c r="G56" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="H56">
         <v>1</v>
       </c>
       <c r="I56" t="s">
-        <v>989</v>
+        <v>992</v>
       </c>
       <c r="J56" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="K56" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="L56" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="B57" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C57" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="D57" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E57" t="s">
-        <v>994</v>
+        <v>997</v>
       </c>
       <c r="F57" t="s">
-        <v>995</v>
+        <v>998</v>
       </c>
       <c r="G57" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="H57">
         <v>2</v>
       </c>
       <c r="I57" t="s">
-        <v>996</v>
+        <v>999</v>
       </c>
       <c r="J57" t="s">
-        <v>997</v>
+        <v>1000</v>
       </c>
       <c r="K57" t="s">
-        <v>998</v>
+        <v>1001</v>
       </c>
       <c r="L57" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>1000</v>
+        <v>1003</v>
       </c>
       <c r="B58" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="C58" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="D58" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E58" t="s">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="F58" t="s">
-        <v>1002</v>
+        <v>1005</v>
       </c>
       <c r="G58" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="H58">
         <v>2</v>
       </c>
       <c r="I58" t="s">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="J58" t="s">
-        <v>1004</v>
+        <v>1007</v>
       </c>
       <c r="K58" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
       <c r="L58" t="s">
-        <v>1006</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>1007</v>
+        <v>1010</v>
       </c>
       <c r="B59" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="C59" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="D59" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E59" t="s">
-        <v>1008</v>
+        <v>1011</v>
       </c>
       <c r="F59" t="s">
-        <v>1009</v>
+        <v>1012</v>
       </c>
       <c r="G59" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="H59">
         <v>1</v>
       </c>
       <c r="I59" t="s">
-        <v>1010</v>
+        <v>1013</v>
       </c>
       <c r="J59" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="K59" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="L59" t="s">
-        <v>1013</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
       <c r="B60" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C60" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="D60" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E60" t="s">
-        <v>1015</v>
+        <v>1018</v>
       </c>
       <c r="F60" t="s">
-        <v>1016</v>
+        <v>1019</v>
       </c>
       <c r="G60" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="H60">
         <v>2</v>
       </c>
       <c r="I60" t="s">
-        <v>1017</v>
+        <v>1020</v>
       </c>
       <c r="J60" t="s">
-        <v>1018</v>
+        <v>1021</v>
       </c>
       <c r="K60" t="s">
-        <v>1019</v>
+        <v>1022</v>
       </c>
       <c r="L60" t="s">
-        <v>1020</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>1021</v>
+        <v>1024</v>
       </c>
       <c r="B61" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C61" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="D61" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E61" t="s">
-        <v>1022</v>
+        <v>1025</v>
       </c>
       <c r="F61" t="s">
-        <v>1023</v>
+        <v>1026</v>
       </c>
       <c r="G61" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="H61">
         <v>2</v>
       </c>
       <c r="I61" t="s">
-        <v>1024</v>
+        <v>1027</v>
       </c>
       <c r="J61" t="s">
-        <v>1025</v>
+        <v>1028</v>
       </c>
       <c r="K61" t="s">
-        <v>1026</v>
+        <v>1029</v>
       </c>
       <c r="L61" t="s">
-        <v>1027</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>1028</v>
+        <v>1031</v>
       </c>
       <c r="B62" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="C62" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="D62" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E62" t="s">
-        <v>1029</v>
+        <v>1032</v>
       </c>
       <c r="F62" t="s">
-        <v>1030</v>
+        <v>1033</v>
       </c>
       <c r="G62" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="H62">
         <v>1</v>
       </c>
       <c r="I62" t="s">
-        <v>1031</v>
+        <v>1034</v>
       </c>
       <c r="J62" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="K62" t="s">
-        <v>1032</v>
+        <v>1035</v>
       </c>
       <c r="L62" t="s">
-        <v>1033</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>1034</v>
+        <v>1037</v>
       </c>
       <c r="B63" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="C63" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="D63" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E63" t="s">
-        <v>1035</v>
+        <v>1038</v>
       </c>
       <c r="F63" t="s">
-        <v>1036</v>
+        <v>1039</v>
       </c>
       <c r="G63" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="H63">
         <v>1</v>
       </c>
       <c r="I63" t="s">
-        <v>1037</v>
+        <v>1040</v>
       </c>
       <c r="J63" t="s">
-        <v>1038</v>
+        <v>1041</v>
       </c>
       <c r="K63" t="s">
-        <v>1039</v>
+        <v>1042</v>
       </c>
       <c r="L63" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="B64" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C64" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="D64" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E64" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="F64" t="s">
-        <v>1043</v>
+        <v>1046</v>
       </c>
       <c r="G64" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="H64">
         <v>2</v>
       </c>
       <c r="I64" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="J64" t="s">
-        <v>1045</v>
+        <v>1048</v>
       </c>
       <c r="K64" t="s">
-        <v>1046</v>
+        <v>1049</v>
       </c>
       <c r="L64" t="s">
-        <v>1047</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>1048</v>
+        <v>1051</v>
       </c>
       <c r="B65" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C65" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="D65" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E65" t="s">
-        <v>1049</v>
+        <v>1052</v>
       </c>
       <c r="F65" t="s">
-        <v>1050</v>
+        <v>1053</v>
       </c>
       <c r="G65" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="H65">
         <v>1</v>
       </c>
       <c r="I65" t="s">
-        <v>1051</v>
+        <v>1054</v>
       </c>
       <c r="J65" t="s">
-        <v>1052</v>
+        <v>1055</v>
       </c>
       <c r="K65" t="s">
-        <v>1053</v>
+        <v>1056</v>
       </c>
       <c r="L65" t="s">
-        <v>1054</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>1055</v>
+        <v>1058</v>
       </c>
       <c r="B66" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="C66" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="D66" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E66" t="s">
-        <v>1056</v>
+        <v>1059</v>
       </c>
       <c r="F66" t="s">
-        <v>1057</v>
+        <v>1060</v>
       </c>
       <c r="G66" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="H66">
         <v>2</v>
       </c>
       <c r="I66" t="s">
-        <v>1058</v>
+        <v>1061</v>
       </c>
       <c r="J66" t="s">
-        <v>1059</v>
+        <v>1062</v>
       </c>
       <c r="K66" t="s">
-        <v>1060</v>
+        <v>1063</v>
       </c>
       <c r="L66" t="s">
-        <v>1061</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>1062</v>
+        <v>1065</v>
       </c>
       <c r="B67" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="C67" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="D67" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E67" t="s">
-        <v>1056</v>
+        <v>1059</v>
       </c>
       <c r="F67" t="s">
-        <v>1063</v>
+        <v>1066</v>
       </c>
       <c r="G67" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="H67">
         <v>1</v>
       </c>
       <c r="I67" t="s">
-        <v>1064</v>
+        <v>1067</v>
       </c>
       <c r="J67" t="s">
-        <v>1065</v>
+        <v>1068</v>
       </c>
       <c r="K67" t="s">
-        <v>1066</v>
+        <v>1069</v>
       </c>
       <c r="L67" t="s">
-        <v>1067</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>1068</v>
+        <v>1071</v>
       </c>
       <c r="B68" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="C68" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="D68" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E68" t="s">
-        <v>1069</v>
+        <v>1072</v>
       </c>
       <c r="F68" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="G68" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="H68">
         <v>2</v>
       </c>
       <c r="I68" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="J68" t="s">
-        <v>1072</v>
+        <v>1075</v>
       </c>
       <c r="K68" t="s">
-        <v>1073</v>
+        <v>1076</v>
       </c>
       <c r="L68" t="s">
-        <v>1074</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>1075</v>
+        <v>1078</v>
       </c>
       <c r="B69" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="C69" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="D69" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E69" t="s">
-        <v>1076</v>
+        <v>1079</v>
       </c>
       <c r="F69" t="s">
-        <v>1077</v>
+        <v>1080</v>
       </c>
       <c r="G69" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="H69">
         <v>2</v>
       </c>
       <c r="I69" t="s">
-        <v>1078</v>
+        <v>1081</v>
       </c>
       <c r="J69" t="s">
-        <v>1079</v>
+        <v>1082</v>
       </c>
       <c r="K69" t="s">
-        <v>1080</v>
+        <v>1083</v>
       </c>
       <c r="L69" t="s">
-        <v>1027</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>1081</v>
+        <v>1084</v>
       </c>
       <c r="B70" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="C70" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D70" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E70" t="s">
-        <v>1082</v>
+        <v>1085</v>
       </c>
       <c r="F70" t="s">
-        <v>1083</v>
+        <v>1086</v>
       </c>
       <c r="G70" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="H70">
         <v>1</v>
       </c>
       <c r="I70" t="s">
-        <v>1084</v>
+        <v>1087</v>
       </c>
       <c r="J70" t="s">
-        <v>1085</v>
+        <v>1088</v>
       </c>
       <c r="K70" t="s">
-        <v>1086</v>
+        <v>1089</v>
       </c>
       <c r="L70" t="s">
-        <v>1087</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>1088</v>
+        <v>1091</v>
       </c>
       <c r="B71" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="C71" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="D71" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E71" t="s">
-        <v>1089</v>
+        <v>1092</v>
       </c>
       <c r="F71" t="s">
-        <v>1090</v>
+        <v>1093</v>
       </c>
       <c r="G71" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="H71">
         <v>1</v>
       </c>
       <c r="I71" t="s">
-        <v>1091</v>
+        <v>1094</v>
       </c>
       <c r="J71" t="s">
-        <v>1092</v>
+        <v>1095</v>
       </c>
       <c r="K71" t="s">
-        <v>1093</v>
+        <v>1096</v>
       </c>
       <c r="L71" t="s">
-        <v>1094</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>1095</v>
+        <v>1098</v>
       </c>
       <c r="B72" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="C72" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="D72" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E72" t="s">
-        <v>1096</v>
+        <v>1099</v>
       </c>
       <c r="F72" t="s">
-        <v>1097</v>
+        <v>1100</v>
       </c>
       <c r="G72" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="H72">
         <v>3</v>
       </c>
       <c r="I72" t="s">
-        <v>933</v>
+        <v>936</v>
       </c>
       <c r="J72" t="s">
-        <v>1098</v>
+        <v>1101</v>
       </c>
       <c r="K72" t="s">
-        <v>1099</v>
+        <v>1102</v>
       </c>
       <c r="L72" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>1100</v>
+        <v>1103</v>
       </c>
       <c r="B73" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="C73" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="D73" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E73" t="s">
-        <v>1101</v>
+        <v>1104</v>
       </c>
       <c r="F73" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
       <c r="G73" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="H73">
         <v>2</v>
       </c>
       <c r="I73" t="s">
-        <v>1103</v>
+        <v>1106</v>
       </c>
       <c r="J73" t="s">
-        <v>1104</v>
+        <v>1107</v>
       </c>
       <c r="K73" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="L73" t="s">
-        <v>1106</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>1107</v>
+        <v>1110</v>
       </c>
       <c r="B74" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C74" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="D74" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E74" t="s">
-        <v>1108</v>
+        <v>1111</v>
       </c>
       <c r="F74" t="s">
-        <v>1109</v>
+        <v>1112</v>
       </c>
       <c r="G74" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="H74">
         <v>2</v>
       </c>
       <c r="I74" t="s">
-        <v>1110</v>
+        <v>1113</v>
       </c>
       <c r="J74" t="s">
-        <v>1111</v>
+        <v>1114</v>
       </c>
       <c r="K74" t="s">
-        <v>1112</v>
+        <v>1115</v>
       </c>
       <c r="L74" t="s">
-        <v>1113</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>1114</v>
+        <v>1117</v>
       </c>
       <c r="B75" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="C75" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="D75" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E75" t="s">
-        <v>1115</v>
+        <v>1118</v>
       </c>
       <c r="F75" t="s">
-        <v>1116</v>
+        <v>1119</v>
       </c>
       <c r="G75" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="H75">
         <v>3</v>
       </c>
       <c r="I75" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
       <c r="J75" t="s">
-        <v>1118</v>
+        <v>1121</v>
       </c>
       <c r="K75" t="s">
-        <v>1119</v>
+        <v>1122</v>
       </c>
       <c r="L75" t="s">
-        <v>1120</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>1121</v>
+        <v>1124</v>
       </c>
       <c r="B76" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="C76" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="D76" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E76" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="F76" t="s">
-        <v>1123</v>
+        <v>1126</v>
       </c>
       <c r="G76" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="H76">
         <v>1</v>
       </c>
       <c r="I76" t="s">
-        <v>1124</v>
+        <v>1127</v>
       </c>
       <c r="J76" t="s">
-        <v>1125</v>
+        <v>1128</v>
       </c>
       <c r="K76" t="s">
-        <v>1126</v>
+        <v>1129</v>
       </c>
       <c r="L76" t="s">
-        <v>1006</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>1127</v>
+        <v>1130</v>
       </c>
       <c r="B77" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="C77" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D77" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E77" t="s">
-        <v>1128</v>
+        <v>1131</v>
       </c>
       <c r="F77" t="s">
-        <v>1129</v>
+        <v>1132</v>
       </c>
       <c r="G77" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="H77">
         <v>3</v>
       </c>
       <c r="I77" t="s">
-        <v>1130</v>
+        <v>1133</v>
       </c>
       <c r="J77" t="s">
-        <v>1131</v>
+        <v>1134</v>
       </c>
       <c r="K77" t="s">
-        <v>1132</v>
+        <v>1135</v>
       </c>
       <c r="L77" t="s">
-        <v>1133</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>1134</v>
+        <v>1137</v>
       </c>
       <c r="B78" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="C78" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="D78" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E78" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="F78" t="s">
-        <v>1136</v>
+        <v>1139</v>
       </c>
       <c r="G78" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="H78">
         <v>3</v>
       </c>
       <c r="I78" t="s">
-        <v>1137</v>
+        <v>1140</v>
       </c>
       <c r="J78" t="s">
-        <v>1138</v>
+        <v>1141</v>
       </c>
       <c r="K78" t="s">
-        <v>1139</v>
+        <v>1142</v>
       </c>
       <c r="L78" t="s">
-        <v>1133</v>
+        <v>1136</v>
       </c>
     </row>
   </sheetData>
@@ -9667,18 +10036,18 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>1140</v>
+        <v>1143</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>1141</v>
+        <v>1144</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>1142</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1143</v>
+        <v>1146</v>
       </c>
       <c r="B2">
         <f>SUMPRODUCT((COUNTIF(NODOS!A2:A500,NODOS!A2:A500)&gt;1)*(NODOS!A2:A500&lt;&gt;""))</f>
@@ -9689,7 +10058,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1144</v>
+        <v>1147</v>
       </c>
       <c r="B3">
         <f>SUMPRODUCT((NODOS!A2:A500&lt;&gt;"")*(COUNTIF(CAPAS!B2:B30,NODOS!C2:C500)=0))</f>
@@ -9700,7 +10069,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1145</v>
+        <v>1148</v>
       </c>
       <c r="B4">
         <f>SUMPRODUCT((ARISTAS!A2:A500&lt;&gt;"")*(COUNTIF(NODOS!A2:A500,ARISTAS!B2:B500)=0))</f>
@@ -9711,7 +10080,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1146</v>
+        <v>1149</v>
       </c>
       <c r="B5">
         <f>SUMPRODUCT((ARISTAS!A2:A500&lt;&gt;"")*(COUNTIF(NODOS!A2:A500,ARISTAS!C2:C500)=0))</f>
@@ -9722,7 +10091,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1147</v>
+        <v>1150</v>
       </c>
       <c r="B6">
         <f>SUMPRODUCT((ARISTAS!A2:A500&lt;&gt;"")*(COUNTIF(INTERACCIONES!B2:B30,ARISTAS!D2:D500)=0))</f>
@@ -9733,7 +10102,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1148</v>
+        <v>1151</v>
       </c>
       <c r="B7">
         <f>SUMPRODUCT((ARISTAS!A2:A500&lt;&gt;"")*(ARISTAS!B2:B500=ARISTAS!C2:C500))</f>
@@ -9744,7 +10113,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1149</v>
+        <v>1152</v>
       </c>
       <c r="B8">
         <f>SUMPRODUCT((NODOS!A2:A500&lt;&gt;"")*(COUNTIF(ARISTAS!B2:B500,NODOS!A2:A500)+COUNTIF(ARISTAS!C2:C500,NODOS!A2:A500)=0))</f>
@@ -9755,7 +10124,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1150</v>
+        <v>1153</v>
       </c>
       <c r="B9" t="s">
         <v>1</v>
@@ -9766,7 +10135,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1151</v>
+        <v>1154</v>
       </c>
       <c r="B10">
         <f>COUNTA(NODOS!A2:A500)</f>
@@ -9774,7 +10143,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1152</v>
+        <v>1155</v>
       </c>
       <c r="B11">
         <f>COUNTA(ARISTAS!A2:A500)</f>

--- a/datos/red-pot-kennedy-visor.xlsx
+++ b/datos/red-pot-kennedy-visor.xlsx
@@ -10,13 +10,14 @@
     <sheet sheetId="4" name="NODOS" state="visible" r:id="rId7"/>
     <sheet sheetId="5" name="ARISTAS" state="visible" r:id="rId8"/>
     <sheet sheetId="6" name="CONTROL" state="visible" r:id="rId9"/>
+    <sheet sheetId="7" name="RED" state="visible" r:id="rId10"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1696" uniqueCount="1156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1718" uniqueCount="1178">
   <si>
     <t>RED POT KENNEDY - DATOS DEL VISOR 3D</t>
   </si>
@@ -3484,6 +3485,72 @@
   </si>
   <si>
     <t>Total aristas</t>
+  </si>
+  <si>
+    <t>Clave</t>
+  </si>
+  <si>
+    <t>Valor</t>
+  </si>
+  <si>
+    <t>titulo</t>
+  </si>
+  <si>
+    <t>Red Territorial de Kennedy (POT) — Sistema Socioecológico</t>
+  </si>
+  <si>
+    <t>marca</t>
+  </si>
+  <si>
+    <t>RED TERRITORIAL DE KENNEDY (POT)</t>
+  </si>
+  <si>
+    <t>faq1_pregunta</t>
+  </si>
+  <si>
+    <t>¿Qué significan las relaciones entre nodos?</t>
+  </si>
+  <si>
+    <t>faq1_respuesta</t>
+  </si>
+  <si>
+    <t>Cada enlace es una relación territorial con justificación causal: articulación funcional, presión ecológica, fragmentación, encadenamiento económico, desplazamiento, soporte ecosistémico, gestión institucional o gobernanza. Se basan en el POT (Decreto 555 de 2021) y en evidencia local de Kennedy.</t>
+  </si>
+  <si>
+    <t>faq2_pregunta</t>
+  </si>
+  <si>
+    <t>¿Por qué la infraestructura presiona los humedales?</t>
+  </si>
+  <si>
+    <t>faq2_respuesta</t>
+  </si>
+  <si>
+    <t>Corabastos, la Av. Ciudad de Cali y el sellamiento del suelo externalizan costos (ruido, lixiviados, escorrentía) sobre El Burro, La Vaca y Techo, que el POT trata como polígonos aislados.</t>
+  </si>
+  <si>
+    <t>faq3_pregunta</t>
+  </si>
+  <si>
+    <t>¿Qué dice el POT y qué ocurre en el territorio?</t>
+  </si>
+  <si>
+    <t>faq3_respuesta</t>
+  </si>
+  <si>
+    <t>Cada relación contrasta la intención declarada por la norma con su efecto operativo real; las hipótesis se formulan con base en el Decreto 555 y en la evidencia territorial de cada conexión.</t>
+  </si>
+  <si>
+    <t>faq4_pregunta</t>
+  </si>
+  <si>
+    <t>¿Qué tensiones son críticas?</t>
+  </si>
+  <si>
+    <t>faq4_respuesta</t>
+  </si>
+  <si>
+    <t>Las de nivel crítico: la Av. Ciudad de Cali partiendo El Burro, los vertimientos de Corabastos sobre La Vaca, la remoción de arbolado hub y el ruido sobre la fauna endémica. Filtra por tipo de relación para verlas en la red.</t>
   </si>
 </sst>
 </file>
@@ -10153,4 +10220,107 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="120" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1157</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1158</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1159</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>1160</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1161</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>1162</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1163</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>1164</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>1166</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1167</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>1168</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1169</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>1170</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1171</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>1172</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1173</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B10" t="s">
+        <v>1175</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1177</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
 </file>
--- a/datos/red-pot-kennedy-visor.xlsx
+++ b/datos/red-pot-kennedy-visor.xlsx
@@ -4096,7 +4096,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -4295,7 +4295,7 @@
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -4466,7 +4466,7 @@
   </sheetData>
   <autoFilter ref="A1:E1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -4570,10 +4570,10 @@
         <v>1</v>
       </c>
       <c r="M2">
-        <v>4.656</v>
+        <v>4.66159</v>
       </c>
       <c r="N2">
-        <v>-74.14</v>
+        <v>-74.13137</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
@@ -4614,10 +4614,10 @@
         <v>1</v>
       </c>
       <c r="M3">
-        <v>4.63</v>
+        <v>4.63433</v>
       </c>
       <c r="N3">
-        <v>-74.157</v>
+        <v>-74.15546</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
@@ -4658,10 +4658,10 @@
         <v>1</v>
       </c>
       <c r="M4">
-        <v>4.615</v>
+        <v>4.61862</v>
       </c>
       <c r="N4">
-        <v>-74.174</v>
+        <v>-74.17954</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
@@ -4702,10 +4702,10 @@
         <v>1</v>
       </c>
       <c r="M5">
-        <v>4.6255</v>
+        <v>4.62962</v>
       </c>
       <c r="N5">
-        <v>-74.16</v>
+        <v>-74.15972</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
@@ -4746,10 +4746,10 @@
         <v>1</v>
       </c>
       <c r="M6">
-        <v>4.636</v>
+        <v>4.64062</v>
       </c>
       <c r="N6">
-        <v>-74.153</v>
+        <v>-74.14979</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
@@ -4790,10 +4790,10 @@
         <v>1</v>
       </c>
       <c r="M7">
-        <v>4.6249</v>
+        <v>4.62899</v>
       </c>
       <c r="N7">
-        <v>-74.162</v>
+        <v>-74.16255</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
@@ -4834,10 +4834,10 @@
         <v>1</v>
       </c>
       <c r="M8">
-        <v>4.6419</v>
+        <v>4.64681</v>
       </c>
       <c r="N8">
-        <v>-74.1478</v>
+        <v>-74.14243</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
@@ -4878,10 +4878,10 @@
         <v>1</v>
       </c>
       <c r="M9">
-        <v>4.6262</v>
+        <v>4.63034</v>
       </c>
       <c r="N9">
-        <v>-74.1514</v>
+        <v>-74.14754</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
@@ -4922,10 +4922,10 @@
         <v>1</v>
       </c>
       <c r="M10">
-        <v>4.612</v>
+        <v>4.61548</v>
       </c>
       <c r="N10">
-        <v>-74.176</v>
+        <v>-74.18238</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
@@ -4966,10 +4966,10 @@
         <v>1</v>
       </c>
       <c r="M11">
-        <v>4.63</v>
+        <v>4.63432</v>
       </c>
       <c r="N11">
-        <v>-74.15</v>
+        <v>-74.14556</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
@@ -5010,10 +5010,10 @@
         <v>1</v>
       </c>
       <c r="M12">
-        <v>4.633</v>
+        <v>4.63746</v>
       </c>
       <c r="N12">
-        <v>-74.144</v>
+        <v>-74.13706</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
@@ -5054,10 +5054,10 @@
         <v>1</v>
       </c>
       <c r="M13">
-        <v>4.635</v>
+        <v>4.63958</v>
       </c>
       <c r="N13">
-        <v>-74.1545</v>
+        <v>-74.15192</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
@@ -5098,10 +5098,10 @@
         <v>1</v>
       </c>
       <c r="M14">
-        <v>4.633</v>
+        <v>4.63745</v>
       </c>
       <c r="N14">
-        <v>-74.138</v>
+        <v>-74.12857</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
@@ -5142,10 +5142,10 @@
         <v>1</v>
       </c>
       <c r="M15">
-        <v>4.629</v>
+        <v>4.63329</v>
       </c>
       <c r="N15">
-        <v>-74.159</v>
+        <v>-74.1583</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
@@ -5186,10 +5186,10 @@
         <v>1</v>
       </c>
       <c r="M16">
-        <v>4.614</v>
+        <v>4.61757</v>
       </c>
       <c r="N16">
-        <v>-74.17</v>
+        <v>-74.17388</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
@@ -5230,10 +5230,10 @@
         <v>1</v>
       </c>
       <c r="M17">
-        <v>4.6225</v>
+        <v>4.62647</v>
       </c>
       <c r="N17">
-        <v>-74.159</v>
+        <v>-74.1583</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
@@ -5274,10 +5274,10 @@
         <v>1</v>
       </c>
       <c r="M18">
-        <v>4.64</v>
+        <v>4.6448</v>
       </c>
       <c r="N18">
-        <v>-74.14</v>
+        <v>-74.13139</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
@@ -5318,10 +5318,10 @@
         <v>1</v>
       </c>
       <c r="M19">
-        <v>4.621</v>
+        <v>4.62489</v>
       </c>
       <c r="N19">
-        <v>-74.154</v>
+        <v>-74.15123</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
@@ -5362,10 +5362,10 @@
         <v>1</v>
       </c>
       <c r="M20">
-        <v>4.623</v>
+        <v>4.62697</v>
       </c>
       <c r="N20">
-        <v>-74.148</v>
+        <v>-74.14273</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
@@ -5406,10 +5406,10 @@
         <v>1</v>
       </c>
       <c r="M21">
-        <v>4.6335</v>
+        <v>4.638</v>
       </c>
       <c r="N21">
-        <v>-74.155</v>
+        <v>-74.15263</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
@@ -5450,10 +5450,10 @@
         <v>1</v>
       </c>
       <c r="M22">
-        <v>4.6365</v>
+        <v>4.64115</v>
       </c>
       <c r="N22">
-        <v>-74.152</v>
+        <v>-74.14838</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
@@ -5494,10 +5494,10 @@
         <v>1</v>
       </c>
       <c r="M23">
-        <v>4.637</v>
+        <v>4.64167</v>
       </c>
       <c r="N23">
-        <v>-74.154</v>
+        <v>-74.15121</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
@@ -5538,10 +5538,10 @@
         <v>1</v>
       </c>
       <c r="M24">
-        <v>4.626</v>
+        <v>4.63014</v>
       </c>
       <c r="N24">
-        <v>-74.156</v>
+        <v>-74.15405</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
@@ -5582,10 +5582,10 @@
         <v>1</v>
       </c>
       <c r="M25">
-        <v>4.6355</v>
+        <v>4.6401</v>
       </c>
       <c r="N25">
-        <v>-74.1535</v>
+        <v>-74.1505</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
@@ -5626,10 +5626,10 @@
         <v>1</v>
       </c>
       <c r="M26">
-        <v>4.6345</v>
+        <v>4.63904</v>
       </c>
       <c r="N26">
-        <v>-74.15</v>
+        <v>-74.14555</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
@@ -5670,10 +5670,10 @@
         <v>1</v>
       </c>
       <c r="M27">
-        <v>4.6245</v>
+        <v>4.62857</v>
       </c>
       <c r="N27">
-        <v>-74.161</v>
+        <v>-74.16113</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
@@ -5714,10 +5714,10 @@
         <v>1</v>
       </c>
       <c r="M28">
-        <v>4.634</v>
+        <v>4.63853</v>
       </c>
       <c r="N28">
-        <v>-74.156</v>
+        <v>-74.15404</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
@@ -5758,10 +5758,10 @@
         <v>1</v>
       </c>
       <c r="M29">
-        <v>4.626</v>
+        <v>4.63012</v>
       </c>
       <c r="N29">
-        <v>-74.145</v>
+        <v>-74.13848</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
@@ -5802,10 +5802,10 @@
         <v>1</v>
       </c>
       <c r="M30">
-        <v>4.631</v>
+        <v>4.63539</v>
       </c>
       <c r="N30">
-        <v>-74.16</v>
+        <v>-74.15971</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
@@ -5846,10 +5846,10 @@
         <v>1</v>
       </c>
       <c r="M31">
-        <v>4.638</v>
+        <v>4.64272</v>
       </c>
       <c r="N31">
-        <v>-74.15</v>
+        <v>-74.14555</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
@@ -5890,10 +5890,10 @@
         <v>1</v>
       </c>
       <c r="M32">
-        <v>4.627</v>
+        <v>4.63117</v>
       </c>
       <c r="N32">
-        <v>-74.148</v>
+        <v>-74.14273</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
@@ -5934,10 +5934,10 @@
         <v>1</v>
       </c>
       <c r="M33">
-        <v>4.6285</v>
+        <v>4.63275</v>
       </c>
       <c r="N33">
-        <v>-74.153</v>
+        <v>-74.1498</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
@@ -5978,10 +5978,10 @@
         <v>1</v>
       </c>
       <c r="M34">
-        <v>4.6125</v>
+        <v>4.61597</v>
       </c>
       <c r="N34">
-        <v>-74.155</v>
+        <v>-74.15265</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
@@ -6022,10 +6022,10 @@
         <v>1</v>
       </c>
       <c r="M35">
-        <v>4.646</v>
+        <v>4.6511</v>
       </c>
       <c r="N35">
-        <v>-74.145</v>
+        <v>-74.13846</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
@@ -6066,10 +6066,10 @@
         <v>1</v>
       </c>
       <c r="M36">
-        <v>4.63</v>
+        <v>4.63434</v>
       </c>
       <c r="N36">
-        <v>-74.1575</v>
+        <v>-74.15617</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
@@ -6110,10 +6110,10 @@
         <v>1</v>
       </c>
       <c r="M37">
-        <v>4.6215</v>
+        <v>4.6254</v>
       </c>
       <c r="N37">
-        <v>-74.149</v>
+        <v>-74.14415</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
@@ -6154,10 +6154,10 @@
         <v>1</v>
       </c>
       <c r="M38">
-        <v>4.617</v>
+        <v>4.62072</v>
       </c>
       <c r="N38">
-        <v>-74.17</v>
+        <v>-74.17388</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
@@ -6198,10 +6198,10 @@
         <v>1</v>
       </c>
       <c r="M39">
-        <v>4.634</v>
+        <v>4.63854</v>
       </c>
       <c r="N39">
-        <v>-74.1595</v>
+        <v>-74.159</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
@@ -6242,10 +6242,10 @@
         <v>1</v>
       </c>
       <c r="M40">
-        <v>4.62</v>
+        <v>4.62383</v>
       </c>
       <c r="N40">
-        <v>-74.152</v>
+        <v>-74.1484</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
@@ -6286,10 +6286,10 @@
         <v>1</v>
       </c>
       <c r="M41">
-        <v>4.624</v>
+        <v>4.62802</v>
       </c>
       <c r="N41">
-        <v>-74.144</v>
+        <v>-74.13707</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
@@ -6330,10 +6330,10 @@
         <v>1</v>
       </c>
       <c r="M42">
-        <v>4.631</v>
+        <v>4.63535</v>
       </c>
       <c r="N42">
-        <v>-74.137</v>
+        <v>-74.12716</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
@@ -6374,10 +6374,10 @@
         <v>1</v>
       </c>
       <c r="M43">
-        <v>4.613</v>
+        <v>4.61648</v>
       </c>
       <c r="N43">
-        <v>-74.15</v>
+        <v>-74.14558</v>
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
@@ -6418,10 +6418,10 @@
         <v>1</v>
       </c>
       <c r="M44">
-        <v>4.619</v>
+        <v>4.6228</v>
       </c>
       <c r="N44">
-        <v>-74.159</v>
+        <v>-74.15831</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
@@ -6462,10 +6462,10 @@
         <v>1</v>
       </c>
       <c r="M45">
-        <v>4.632</v>
+        <v>4.63641</v>
       </c>
       <c r="N45">
-        <v>-74.142</v>
+        <v>-74.13423</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
@@ -6506,10 +6506,10 @@
         <v>1</v>
       </c>
       <c r="M46">
-        <v>4.645</v>
+        <v>4.65005</v>
       </c>
       <c r="N46">
-        <v>-74.145</v>
+        <v>-74.13846</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
@@ -6550,10 +6550,10 @@
         <v>1</v>
       </c>
       <c r="M47">
-        <v>4.6368</v>
+        <v>4.64146</v>
       </c>
       <c r="N47">
-        <v>-74.1522</v>
+        <v>-74.14866</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
@@ -6594,10 +6594,10 @@
         <v>1</v>
       </c>
       <c r="M48">
-        <v>4.64</v>
+        <v>4.64482</v>
       </c>
       <c r="N48">
-        <v>-74.15</v>
+        <v>-74.14554</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
@@ -6638,10 +6638,10 @@
         <v>1</v>
       </c>
       <c r="M49">
-        <v>4.654</v>
+        <v>4.6595</v>
       </c>
       <c r="N49">
-        <v>-74.145</v>
+        <v>-74.13845</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
@@ -6682,10 +6682,10 @@
         <v>1</v>
       </c>
       <c r="M50">
-        <v>4.631</v>
+        <v>4.63539</v>
       </c>
       <c r="N50">
-        <v>-74.163</v>
+        <v>-74.16395</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
@@ -6726,10 +6726,10 @@
         <v>1</v>
       </c>
       <c r="M51">
-        <v>4.611</v>
+        <v>4.61442</v>
       </c>
       <c r="N51">
-        <v>-74.173</v>
+        <v>-74.17813</v>
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
@@ -6770,10 +6770,10 @@
         <v>1</v>
       </c>
       <c r="M52">
-        <v>4.62</v>
+        <v>4.62386</v>
       </c>
       <c r="N52">
-        <v>-74.17</v>
+        <v>-74.17388</v>
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
@@ -6814,10 +6814,10 @@
         <v>1</v>
       </c>
       <c r="M53">
-        <v>4.6335</v>
+        <v>4.63799</v>
       </c>
       <c r="N53">
-        <v>-74.1465</v>
+        <v>-74.1406</v>
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
@@ -6858,10 +6858,10 @@
         <v>1</v>
       </c>
       <c r="M54">
-        <v>4.628</v>
+        <v>4.63221</v>
       </c>
       <c r="N54">
-        <v>-74.14</v>
+        <v>-74.13141</v>
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
@@ -6902,10 +6902,10 @@
         <v>1</v>
       </c>
       <c r="M55">
-        <v>4.614</v>
+        <v>4.61757</v>
       </c>
       <c r="N55">
-        <v>-74.171</v>
+        <v>-74.1753</v>
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
@@ -6946,10 +6946,10 @@
         <v>1</v>
       </c>
       <c r="M56">
-        <v>4.6352</v>
+        <v>4.63978</v>
       </c>
       <c r="N56">
-        <v>-74.1508</v>
+        <v>-74.14668</v>
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
@@ -6990,10 +6990,10 @@
         <v>1</v>
       </c>
       <c r="M57">
-        <v>4.6365</v>
+        <v>4.64115</v>
       </c>
       <c r="N57">
-        <v>-74.155</v>
+        <v>-74.15262</v>
       </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
@@ -7034,10 +7034,10 @@
         <v>1</v>
       </c>
       <c r="M58">
-        <v>4.6245</v>
+        <v>4.62857</v>
       </c>
       <c r="N58">
-        <v>-74.16</v>
+        <v>-74.15972</v>
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
@@ -7078,21 +7078,24 @@
         <v>1</v>
       </c>
       <c r="M59">
-        <v>4.6235</v>
+        <v>4.62751</v>
       </c>
       <c r="N59">
-        <v>-74.1565</v>
+        <v>-74.15476</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:N1"/>
-  <dataValidations count="1">
+  <dataValidations count="2">
+    <dataValidation type="list" sqref="C10:C259">
+      <formula1>CAPAS!$B$2:$B$30</formula1>
+    </dataValidation>
     <dataValidation type="list" sqref="C2:C259">
       <formula1>CAPAS!$B$2:$B$30</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -10078,16 +10081,22 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:L1"/>
-  <dataValidations count="2">
+  <dataValidations count="4">
+    <dataValidation type="list" sqref="B10:C378">
+      <formula1>NODOS!$A$2:$A$500</formula1>
+    </dataValidation>
     <dataValidation type="list" sqref="B2:C378">
       <formula1>NODOS!$A$2:$A$500</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="D10:D378">
+      <formula1>INTERACCIONES!$B$2:$B$30</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="D2:D378">
       <formula1>INTERACCIONES!$B$2:$B$30</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -10218,7 +10227,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -10321,6 +10330,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/datos/red-pot-kennedy-visor.xlsx
+++ b/datos/red-pot-kennedy-visor.xlsx
@@ -661,7 +661,7 @@
     <t>¿El parque lineal del río Bogotá logrará restaurar la planicie de inundación frente al cambio climático?</t>
   </si>
   <si>
-    <t>Consejo de Estado, Sección Primera, sentencia del 28 de marzo de 2014 sobre la cuenca del río Bogotá (acción popular; verificar radicado antes de citar); Decreto 555 de 2021, arts. 60 y 62 (sdp.gov.co/sites/default/files/decreto_555_de_2021.pdf)</t>
+    <t>Consejo de Estado, Sección Primera, sentencia del 28 de marzo de 2014 sobre la cuenca del río Bogotá (acción popular, radicado 25000-23-27-000-2001-90479-01); Decreto 555 de 2021, arts. 60 y 62 (sdp.gov.co/sites/default/files/decreto_555_de_2021.pdf)</t>
   </si>
   <si>
     <t>NOD-EEP06</t>
@@ -1078,7 +1078,7 @@
     <t>¿Por qué el POT no regula umbrales acústicos biofísicos para proteger la fauna en la EEP?</t>
   </si>
   <si>
-    <t>Pinilla, M., Pulido, L. D. y Cardona, C. M. (2024). Evaluación económica de servicios del humedal El Burro, Bogotá. Sociedad y Economía, 51, e10812872 (doi.org/10.25100/sye.v0i51.12872) (unas 83 especies de fauna registradas, SDA 2021); Secretaría Distrital de Ambiente, Plan de Manejo Ambiental del humedal El Burro, formulado por el IDEA de la Universidad Nacional (ambientebogota.gov.co/documents/10184/804589/PMA+EL+BURRO.pdf); estado de amenaza de Rallus semiplumbeus: verificar en el listado de especies amenazadas del Ministerio de Ambiente (Resolución 1912 de 2017)</t>
+    <t>Pinilla, M., Pulido, L. D. y Cardona, C. M. (2024). Evaluación económica de servicios del humedal El Burro, Bogotá. Sociedad y Economía, 51, e10812872 (doi.org/10.25100/sye.v0i51.12872) (unas 83 especies de fauna registradas, SDA 2021); Secretaría Distrital de Ambiente, Plan de Manejo Ambiental del humedal El Burro, formulado por el IDEA de la Universidad Nacional (ambientebogota.gov.co/documents/10184/804589/PMA+EL+BURRO.pdf); Rallus semiplumbeus (tingua bogotana) figura como En Peligro (EN) en BirdLife International/UICN y en el Libro Rojo de Aves de Colombia (Renjifo et al., 2016); Ministerio de Ambiente, Resolución 1912 de 2017 (listado de especies silvestres amenazadas)</t>
   </si>
   <si>
     <t>NOD-BIO02</t>
@@ -1243,7 +1243,7 @@
     <t>¿El manejo hidráulico mecanicista de la EAAB sacrifica la complejidad ecológica del humedal?</t>
   </si>
   <si>
-    <t>Secretaría Distrital de Ambiente, Plan de Manejo Ambiental del humedal El Burro, formulado por el IDEA de la Universidad Nacional (ambientebogota.gov.co/documents/10184/804589/PMA+EL+BURRO.pdf) (la EAAB formula los planes de manejo, convenio 021 de 2005); Alcaldía de Bogotá, EAAB elimina conexiones erradas (bogota.gov.co/mi-ciudad/habitat/acueducto-cierra-conexiones-de-agua-que-contaminaban-rios-de-bogota); Plan de Saneamiento y Manejo de Vertimientos (PSMV) de la EAAB (verificar acto administrativo)</t>
+    <t>Secretaría Distrital de Ambiente, Plan de Manejo Ambiental del humedal El Burro, formulado por el IDEA de la Universidad Nacional (ambientebogota.gov.co/documents/10184/804589/PMA+EL+BURRO.pdf) (la EAAB formula los planes de manejo, convenio 021 de 2005); Alcaldía de Bogotá, EAAB elimina conexiones erradas (bogota.gov.co/mi-ciudad/habitat/acueducto-cierra-conexiones-de-agua-que-contaminaban-rios-de-bogota); Plan de Saneamiento y Manejo de Vertimientos (PSMV) de la EAAB, aprobado por la SDA mediante Resolución 3257 de 2007 y modificado por la Resolución 03428 de 2017</t>
   </si>
   <si>
     <t>fa-faucet</t>
@@ -1546,7 +1546,7 @@
     <t>¿La saturación de Banderas deteriora el tiempo y la calidad de vida de los viajeros?</t>
   </si>
   <si>
-    <t>TransMilenio S.A., Estación Banderas, Troncal Américas (verificar documento oficial)</t>
+    <t>TransMilenio S.A., Estación Banderas, Troncal Américas; estadísticas de oferta y demanda del SITP (transmilenio.gov.co)</t>
   </si>
   <si>
     <t>fa-right-left</t>
@@ -1600,7 +1600,7 @@
     <t>¿La red zonal garantiza accesibilidad equitativa a los barrios periféricos?</t>
   </si>
   <si>
-    <t>TransMilenio S.A., rutas zonales y alimentadoras del SITP (verificar documento oficial)</t>
+    <t>TransMilenio S.A., rutas zonales y alimentadoras del SITP; estadísticas de oferta y demanda (transmilenio.gov.co)</t>
   </si>
   <si>
     <t>fa-van-shuttle</t>
@@ -1792,7 +1792,7 @@
     <t>¿La sentencia se traduce en acciones concretas en el borde de Kennedy?</t>
   </si>
   <si>
-    <t>Consejo de Estado, Sección Primera, sentencia del 28 de marzo de 2014 sobre la cuenca del río Bogotá (acción popular; verificar radicado antes de citar)</t>
+    <t>Consejo de Estado, Sección Primera, sentencia del 28 de marzo de 2014 sobre la cuenca del río Bogotá (acción popular, radicado 25000-23-27-000-2001-90479-01)</t>
   </si>
   <si>
     <t>fa-gavel</t>
@@ -1819,7 +1819,7 @@
     <t>¿La amenaza se refleja en restricciones efectivas o solo en mapas?</t>
   </si>
   <si>
-    <t>Decreto 555 de 2021, art. 18 (amenaza por inundación) y art. 105 (amenaza por inundación en suelo urbano) (sdp.gov.co/sites/default/files/decreto_555_de_2021.pdf); Alcaldía Local de Kennedy (35% del área inundable, redjurista.com, a_jalkennedy_0003_2021); IDIGER: verificar mapas de amenaza</t>
+    <t>Decreto 555 de 2021, art. 18 (amenaza por inundación) y art. 105 (amenaza por inundación en suelo urbano) (sdp.gov.co/sites/default/files/decreto_555_de_2021.pdf); Alcaldía Local de Kennedy (35% del área inundable, redjurista.com, a_jalkennedy_0003_2021); IDIGER, Inundaciones en Bogotá: causas y zonas de riesgo (idiger.gov.co/escenarios-de-riesgo/inundacion/en-bogota); Secretaría Distrital de Salud, ASIS Localidad Kennedy 2024 (saludata.saludcapital.gov.co)</t>
   </si>
   <si>
     <t>fa-house-flood-water</t>
@@ -2005,7 +2005,7 @@
     <t>¿Mientras persistan las conexiones erradas, la regeneración ecológica es posible?</t>
   </si>
   <si>
-    <t>Alcaldía de Bogotá, EAAB, Plan de Identificación y Corrección de Conexiones Erradas (bogota.gov.co/mi-ciudad/habitat/acueducto-cierra-conexiones-de-agua-que-contaminaban-rios-de-bogota); EAAB, PSMV (verificar acto administrativo)</t>
+    <t>Alcaldía de Bogotá, EAAB, Plan de Identificación y Corrección de Conexiones Erradas (bogota.gov.co/mi-ciudad/habitat/acueducto-cierra-conexiones-de-agua-que-contaminaban-rios-de-bogota); EAAB, PSMV: SDA, Resolución 3257 de 2007 y Resolución 03428 de 2017</t>
   </si>
   <si>
     <t>fa-biohazard</t>
